--- a/data/Comparing_Dynamics (1).xlsx
+++ b/data/Comparing_Dynamics (1).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="276">
   <si>
     <t>Datset</t>
   </si>
@@ -737,6 +737,72 @@
     <t>noble-morning-428</t>
   </si>
   <si>
+    <t>noble-forest-468</t>
+  </si>
+  <si>
+    <t>curious-bee-465</t>
+  </si>
+  <si>
+    <t>driven-violet-463</t>
+  </si>
+  <si>
+    <t>peach-valley-457</t>
+  </si>
+  <si>
+    <t>azure-energy-448</t>
+  </si>
+  <si>
+    <t>smart-glitter-470</t>
+  </si>
+  <si>
+    <t>misty-snowball-469</t>
+  </si>
+  <si>
+    <t>winter-cloud-467</t>
+  </si>
+  <si>
+    <t>avid-star-466</t>
+  </si>
+  <si>
+    <t>easy-hill-464</t>
+  </si>
+  <si>
+    <t>vocal-wood-462</t>
+  </si>
+  <si>
+    <t>noble-firebrand-461</t>
+  </si>
+  <si>
+    <t>desert-sky-460</t>
+  </si>
+  <si>
+    <t>misty-energy-459</t>
+  </si>
+  <si>
+    <t>stilted-cloud-458</t>
+  </si>
+  <si>
+    <t>jolly-galaxy-456</t>
+  </si>
+  <si>
+    <t>hearty-plasma-455</t>
+  </si>
+  <si>
+    <t>exalted-oath-454</t>
+  </si>
+  <si>
+    <t>peach-breeze-453</t>
+  </si>
+  <si>
+    <t>pious-hill-451</t>
+  </si>
+  <si>
+    <t>equilibrate_sgd_weight_decay.ipynb</t>
+  </si>
+  <si>
+    <t>Equilibrate with the fluctuation-dissipation relation bit. + weight decay that actually converges!</t>
+  </si>
+  <si>
     <t>equilibrate_sgd_checkpoints.ipynb</t>
   </si>
   <si>
@@ -1335,7 +1401,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:F111" displayName="Table_1" name="Table_1" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:F131" displayName="Table_1" name="Table_1" id="2">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -12777,6 +12843,406 @@
         <v>18</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="B112" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C112" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E112" s="57">
+        <v>49.0</v>
+      </c>
+      <c r="F112" s="43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="B113" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C113" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D113" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E113" s="57">
+        <v>39.0</v>
+      </c>
+      <c r="F113" s="43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="B114" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C114" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D114" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E114" s="57">
+        <v>29.0</v>
+      </c>
+      <c r="F114" s="43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="B115" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C115" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E115" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="F115" s="43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="B116" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C116" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E116" s="57">
+        <v>11.0</v>
+      </c>
+      <c r="F116" s="43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="B117" s="57">
+        <v>1024.0</v>
+      </c>
+      <c r="C117" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D117" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E117" s="57">
+        <v>49.0</v>
+      </c>
+      <c r="F117" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="B118" s="57">
+        <v>1024.0</v>
+      </c>
+      <c r="C118" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D118" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" s="57">
+        <v>39.0</v>
+      </c>
+      <c r="F118" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="B119" s="57">
+        <v>1024.0</v>
+      </c>
+      <c r="C119" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D119" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E119" s="57">
+        <v>29.0</v>
+      </c>
+      <c r="F119" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="B120" s="57">
+        <v>1024.0</v>
+      </c>
+      <c r="C120" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E120" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="F120" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B121" s="57">
+        <v>1024.0</v>
+      </c>
+      <c r="C121" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E121" s="57">
+        <v>11.0</v>
+      </c>
+      <c r="F121" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="B122" s="57">
+        <v>256.0</v>
+      </c>
+      <c r="C122" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E122" s="57">
+        <v>49.0</v>
+      </c>
+      <c r="F122" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="B123" s="57">
+        <v>256.0</v>
+      </c>
+      <c r="C123" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D123" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E123" s="57">
+        <v>39.0</v>
+      </c>
+      <c r="F123" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="B124" s="57">
+        <v>256.0</v>
+      </c>
+      <c r="C124" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D124" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E124" s="57">
+        <v>29.0</v>
+      </c>
+      <c r="F124" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="B125" s="57">
+        <v>256.0</v>
+      </c>
+      <c r="C125" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D125" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E125" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="F125" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="B126" s="57">
+        <v>256.0</v>
+      </c>
+      <c r="C126" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E126" s="57">
+        <v>11.0</v>
+      </c>
+      <c r="F126" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="B127" s="57">
+        <v>128.0</v>
+      </c>
+      <c r="C127" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E127" s="57">
+        <v>49.0</v>
+      </c>
+      <c r="F127" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="B128" s="57">
+        <v>128.0</v>
+      </c>
+      <c r="C128" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D128" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E128" s="57">
+        <v>39.0</v>
+      </c>
+      <c r="F128" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="B129" s="57">
+        <v>128.0</v>
+      </c>
+      <c r="C129" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D129" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E129" s="57">
+        <v>29.0</v>
+      </c>
+      <c r="F129" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" s="57">
+        <v>128.0</v>
+      </c>
+      <c r="C130" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D130" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E130" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="F130" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="B131" s="57">
+        <v>128.0</v>
+      </c>
+      <c r="C131" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D131" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E131" s="57">
+        <v>11.0</v>
+      </c>
+      <c r="F131" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">
@@ -12795,37 +13261,46 @@
     <col customWidth="1" min="1" max="1" width="29.88"/>
   </cols>
   <sheetData>
+    <row r="3">
+      <c r="A3" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>261</v>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="59" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="59" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="60" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" location="scrollTo=bHQrT25j2mZH" ref="A4"/>
-    <hyperlink r:id="rId2" location="scrollTo=fe94d4fc" ref="A5"/>
-    <hyperlink r:id="rId3" location="scrollTo=zrBZV4x86Q3H" ref="A6"/>
+    <hyperlink r:id="rId1" location="scrollTo=29mgvzAuMjkK" ref="A3"/>
+    <hyperlink r:id="rId2" location="scrollTo=bHQrT25j2mZH" ref="A4"/>
+    <hyperlink r:id="rId3" location="scrollTo=fe94d4fc" ref="A5"/>
+    <hyperlink r:id="rId4" location="scrollTo=zrBZV4x86Q3H" ref="A6"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -12898,10 +13373,10 @@
     </row>
     <row r="3">
       <c r="A3" s="62" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
@@ -12930,10 +13405,10 @@
     </row>
     <row r="4">
       <c r="A4" s="63" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
@@ -12962,10 +13437,10 @@
     </row>
     <row r="5">
       <c r="A5" s="64" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -12994,10 +13469,10 @@
     </row>
     <row r="6">
       <c r="A6" s="64" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C6" s="61"/>
       <c r="D6" s="61"/>

--- a/data/Comparing_Dynamics (1).xlsx
+++ b/data/Comparing_Dynamics (1).xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="ICML_runs" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Arkusz5" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Unireps" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Colab" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Literature" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Unireps" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Colab" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Literature" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="MyTodos" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Experiment Groups" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="347">
   <si>
     <t>Datset</t>
   </si>
@@ -797,6 +798,36 @@
     <t>pious-hill-451</t>
   </si>
   <si>
+    <t>resilient-butterfly-492</t>
+  </si>
+  <si>
+    <t>autumn-violet-490</t>
+  </si>
+  <si>
+    <t>usual-meadow-488</t>
+  </si>
+  <si>
+    <t>dark-sound-486</t>
+  </si>
+  <si>
+    <t>helpful-snowflake-482</t>
+  </si>
+  <si>
+    <t>pleasant-paper-477</t>
+  </si>
+  <si>
+    <t>comic-spaceship-476</t>
+  </si>
+  <si>
+    <t>elated-wind-475</t>
+  </si>
+  <si>
+    <t>amber-water-472</t>
+  </si>
+  <si>
+    <t>soft-fog-471</t>
+  </si>
+  <si>
     <t>equilibrate_sgd_weight_decay.ipynb</t>
   </si>
   <si>
@@ -882,12 +913,198 @@
   <si>
     <t>Explains how different single-neuron codes can produce the same representation geometry. Useful for stating precisely that you observe memory of geometry under CKA, rather than preservation of every neuron’s responses or complete functional identity.</t>
   </si>
+  <si>
+    <t xml:space="preserve">Weight Decay 0.01 - Additional High Temperature </t>
+  </si>
+  <si>
+    <t>Plotting exsisting data</t>
+  </si>
+  <si>
+    <t>generate run for the wd 0.01</t>
+  </si>
+  <si>
+    <t>parent-parent similarity within temp vs. accross temperatures (does it ony cover covered distance though)</t>
+  </si>
+  <si>
+    <t>add to wandb</t>
+  </si>
+  <si>
+    <t>quench matching the previous quenching parameter for wd 0.01</t>
+  </si>
+  <si>
+    <t>6thOct_unireps_quench_cka_formatted.ipynb</t>
+  </si>
+  <si>
+    <t>re-generate the plots</t>
+  </si>
+  <si>
+    <t>share your thoughts with michela</t>
+  </si>
+  <si>
+    <t>File Michela sent!</t>
+  </si>
+  <si>
+    <t>put in the overleaf</t>
+  </si>
+  <si>
+    <t>Weight decay 0.003</t>
+  </si>
+  <si>
+    <t>MBJ</t>
+  </si>
+  <si>
+    <t>run low temp</t>
+  </si>
+  <si>
+    <t>maybe repsond saying what we've done. That we agree with him about the overparametrized thing. Plus some questions</t>
+  </si>
+  <si>
+    <t>put in low temp in wandb</t>
+  </si>
+  <si>
+    <t>Maybe questions could be to clarify if he thinks our interpretation is good?</t>
+  </si>
+  <si>
+    <t>analyze the convergence details</t>
+  </si>
+  <si>
+    <t>combined_preparation_diagnostics.ipynb</t>
+  </si>
+  <si>
+    <t>establish good quenching parameter</t>
+  </si>
+  <si>
+    <t>quench low</t>
+  </si>
+  <si>
+    <t>6thOct_WD0.003_unireps_quench_cka_formatted.ipynb</t>
+  </si>
+  <si>
+    <t>generate initial plots</t>
+  </si>
+  <si>
+    <t>analyze results and share with Michela</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>run high temp</t>
+  </si>
+  <si>
+    <t>[ready at 2pm]</t>
+  </si>
+  <si>
+    <t>6Oct_v1_UniReps_stability_wight_decay_v3_experiment_F-MNIST.ipynb</t>
+  </si>
+  <si>
+    <t>measure the actual SGD noise at each parent, instead of relying only on the nominal T = η/B.</t>
+  </si>
+  <si>
+    <t>put high temp in wandb</t>
+  </si>
+  <si>
+    <t>quench the hgih temp</t>
+  </si>
+  <si>
+    <t>generate final plots</t>
+  </si>
+  <si>
+    <t>Put in the overleaf</t>
+  </si>
+  <si>
+    <t>Underparameterized regime</t>
+  </si>
+  <si>
+    <t>decide on model parameters</t>
+  </si>
+  <si>
+    <t>set up and run mock one to decide on number of steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">run all </t>
+  </si>
+  <si>
+    <t>add ro wandb</t>
+  </si>
+  <si>
+    <t>find good quenching parameter</t>
+  </si>
+  <si>
+    <t>recreate the plots</t>
+  </si>
+  <si>
+    <t>analysis and share</t>
+  </si>
+  <si>
+    <t>Put in overleaf?</t>
+  </si>
+  <si>
+    <t>Fashionmnist - unrefgularized</t>
+  </si>
+  <si>
+    <t>fix quench LR</t>
+  </si>
+  <si>
+    <t>Kopia notatnika 6thOct_unireps_quench_cka_formatted.ipynb</t>
+  </si>
+  <si>
+    <t>redo plots</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>weight decay</t>
+  </si>
+  <si>
+    <t>quench LR</t>
+  </si>
+  <si>
+    <t>temperatures</t>
+  </si>
+  <si>
+    <t>extensions of original run?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mnsit </t>
+  </si>
+  <si>
+    <t>fashionmnist</t>
+  </si>
+  <si>
+    <t>fmnist</t>
+  </si>
+  <si>
+    <t>fashion wd big</t>
+  </si>
+  <si>
+    <t>yes, saved in wd_0.01/sgd_continuation_v1</t>
+  </si>
+  <si>
+    <t>fashion wd good</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>mnsit small</t>
+  </si>
+  <si>
+    <t>mnsit</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="21">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -981,8 +1198,20 @@
       <u/>
       <color rgb="FF0000FF"/>
     </font>
+    <font>
+      <i/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1001,8 +1230,38 @@
         <bgColor rgb="FFF6F8F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border/>
     <border>
       <left style="thin">
@@ -1088,11 +1347,25 @@
         <color rgb="FF284E3F"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="77">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1288,6 +1561,28 @@
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="5" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="7" fillId="6" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="8" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="7" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="7" fillId="7" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1382,6 +1677,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
@@ -1401,7 +1700,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:F131" displayName="Table_1" name="Table_1" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:F141" displayName="Table_1" name="Table_1" id="2">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -10608,17 +10907,6 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="17.75"/>
   </cols>
@@ -13240,6 +13528,206 @@
         <v>11.0</v>
       </c>
       <c r="F131" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="B132" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C132" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D132" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E132" s="57">
+        <v>49.0</v>
+      </c>
+      <c r="F132" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="B133" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C133" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D133" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E133" s="57">
+        <v>39.0</v>
+      </c>
+      <c r="F133" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="B134" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C134" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D134" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E134" s="57">
+        <v>29.0</v>
+      </c>
+      <c r="F134" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="B135" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C135" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D135" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E135" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="F135" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="B136" s="57">
+        <v>8.0</v>
+      </c>
+      <c r="C136" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D136" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E136" s="57">
+        <v>11.0</v>
+      </c>
+      <c r="F136" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="B137" s="57">
+        <v>32.0</v>
+      </c>
+      <c r="C137" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D137" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E137" s="57">
+        <v>49.0</v>
+      </c>
+      <c r="F137" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="B138" s="57">
+        <v>32.0</v>
+      </c>
+      <c r="C138" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D138" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E138" s="57">
+        <v>39.0</v>
+      </c>
+      <c r="F138" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="B139" s="57">
+        <v>32.0</v>
+      </c>
+      <c r="C139" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D139" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E139" s="57">
+        <v>29.0</v>
+      </c>
+      <c r="F139" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="B140" s="57">
+        <v>32.0</v>
+      </c>
+      <c r="C140" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D140" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E140" s="57">
+        <v>19.0</v>
+      </c>
+      <c r="F140" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="B141" s="57">
+        <v>32.0</v>
+      </c>
+      <c r="C141" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D141" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E141" s="57">
+        <v>11.0</v>
+      </c>
+      <c r="F141" s="43" t="s">
         <v>71</v>
       </c>
     </row>
@@ -13251,7 +13739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -13263,34 +13751,34 @@
   <sheetData>
     <row r="3">
       <c r="A3" s="59" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="59" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="59" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="60" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -13304,7 +13792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -13373,10 +13861,10 @@
     </row>
     <row r="3">
       <c r="A3" s="62" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C3" s="61"/>
       <c r="D3" s="61"/>
@@ -13405,10 +13893,10 @@
     </row>
     <row r="4">
       <c r="A4" s="63" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
@@ -13437,10 +13925,10 @@
     </row>
     <row r="5">
       <c r="A5" s="64" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C5" s="61"/>
       <c r="D5" s="61"/>
@@ -13469,10 +13957,10 @@
     </row>
     <row r="6">
       <c r="A6" s="64" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C6" s="61"/>
       <c r="D6" s="61"/>
@@ -41340,4 +41828,407 @@
   </hyperlinks>
   <drawing r:id="rId5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="10.75"/>
+    <col customWidth="1" min="2" max="2" width="2.75"/>
+    <col customWidth="1" min="10" max="10" width="2.63"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="65" t="s">
+        <v>286</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="66"/>
+      <c r="C3" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="J3" s="67"/>
+      <c r="K3" s="44" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="66"/>
+      <c r="C4" s="44" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="66"/>
+      <c r="C5" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>292</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="66"/>
+      <c r="C6" s="44" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="66"/>
+      <c r="C7" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="J7" s="68"/>
+      <c r="K7" s="44" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="67"/>
+      <c r="C8" s="44" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="I12" s="65" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="66"/>
+      <c r="C13" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="J13" s="67"/>
+      <c r="K13" s="44" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="66"/>
+      <c r="C14" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="J14" s="67"/>
+      <c r="K14" s="44" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="69"/>
+      <c r="C15" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="E15" s="59" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="66"/>
+      <c r="C16" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="F16" s="70" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="66"/>
+      <c r="C17" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="E17" s="71" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="66"/>
+      <c r="C18" s="44" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="67"/>
+      <c r="C19" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="I19" s="65" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="72"/>
+      <c r="C20" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="D20" s="73" t="s">
+        <v>312</v>
+      </c>
+      <c r="E20" s="71" t="s">
+        <v>313</v>
+      </c>
+      <c r="F20" s="74">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="J20" s="66"/>
+      <c r="K20" s="44" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="72"/>
+      <c r="C21" s="44" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="72"/>
+      <c r="C22" s="44" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="72"/>
+      <c r="C23" s="44" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="72"/>
+      <c r="C24" s="44" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="66"/>
+      <c r="C27" s="44" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="66"/>
+      <c r="C28" s="44" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="75"/>
+      <c r="C29" s="44" t="s">
+        <v>322</v>
+      </c>
+      <c r="D29" s="76"/>
+      <c r="E29" s="71" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="67"/>
+      <c r="C30" s="44" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="67"/>
+      <c r="C31" s="44" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="67"/>
+      <c r="C32" s="44" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="67"/>
+      <c r="C33" s="44" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="67"/>
+      <c r="C34" s="44" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="65" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="66"/>
+      <c r="C38" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="E38" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="F38" s="74">
+        <v>0.6041666666666666</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="67"/>
+      <c r="C39" s="44" t="s">
+        <v>331</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" location="scrollTo=1f15d3a3" ref="E5"/>
+    <hyperlink r:id="rId2" ref="E15"/>
+    <hyperlink r:id="rId3" location="scrollTo=7879018e" ref="E17"/>
+    <hyperlink r:id="rId4" location="scrollTo=DVEXvFBVJL0y" ref="E20"/>
+    <hyperlink r:id="rId5" location="scrollTo=zrBZV4x86Q3H" ref="E29"/>
+    <hyperlink r:id="rId6" location="scrollTo=1f15d3a3" ref="E38"/>
+  </hyperlinks>
+  <drawing r:id="rId7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="18.5"/>
+    <col customWidth="1" min="3" max="3" width="7.88"/>
+    <col customWidth="1" min="4" max="4" width="12.88"/>
+    <col customWidth="1" min="5" max="5" width="8.75"/>
+    <col customWidth="1" min="6" max="6" width="12.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="65" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="65" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" s="65" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="65" t="s">
+        <v>336</v>
+      </c>
+      <c r="F1" s="65" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="44" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="44">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="44">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="44" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="C3" s="44">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="44">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="44">
+        <v>5.0</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="44" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>344</v>
+      </c>
+      <c r="E5" s="44">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="44" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="44">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>344</v>
+      </c>
+      <c r="E6" s="44">
+        <v>4.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/Comparing_Dynamics (1).xlsx
+++ b/data/Comparing_Dynamics (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="513">
   <si>
     <t>Datset</t>
   </si>
@@ -924,9 +924,6 @@
   </si>
   <si>
     <t>crimson-armadillo-507</t>
-  </si>
-  <si>
-    <t>lively-shadow-506</t>
   </si>
   <si>
     <t>mild-violet-505</t>
@@ -15193,31 +15190,17 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="43" t="s">
-        <v>302</v>
-      </c>
-      <c r="B177" s="59">
-        <v>8.0</v>
-      </c>
-      <c r="C177" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D177" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E177" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F177" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G177" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A177" s="43"/>
+      <c r="B177" s="59"/>
+      <c r="C177" s="43"/>
+      <c r="D177" s="62"/>
+      <c r="E177" s="59"/>
+      <c r="F177" s="62"/>
+      <c r="G177" s="62"/>
     </row>
     <row r="178">
       <c r="A178" s="43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B178" s="59">
         <v>1024.0</v>
@@ -15240,7 +15223,7 @@
     </row>
     <row r="179">
       <c r="A179" s="43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B179" s="59">
         <v>1024.0</v>
@@ -15263,7 +15246,7 @@
     </row>
     <row r="180">
       <c r="A180" s="43" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B180" s="59">
         <v>1024.0</v>
@@ -15286,7 +15269,7 @@
     </row>
     <row r="181">
       <c r="A181" s="43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B181" s="59">
         <v>1024.0</v>
@@ -15309,7 +15292,7 @@
     </row>
     <row r="182">
       <c r="A182" s="43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B182" s="59">
         <v>1024.0</v>
@@ -15332,7 +15315,7 @@
     </row>
     <row r="183">
       <c r="A183" s="43" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B183" s="59">
         <v>1024.0</v>
@@ -15700,7 +15683,7 @@
     </row>
     <row r="199">
       <c r="A199" s="43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B199" s="59">
         <v>128.0</v>
@@ -15723,7 +15706,7 @@
     </row>
     <row r="200">
       <c r="A200" s="43" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B200" s="59">
         <v>32.0</v>
@@ -15746,7 +15729,7 @@
     </row>
     <row r="201">
       <c r="A201" s="43" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B201" s="59">
         <v>128.0</v>
@@ -15782,190 +15765,190 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="35.5"/>
+    <col customWidth="1" min="1" max="1" width="56.25"/>
     <col customWidth="1" min="2" max="2" width="14.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="63" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="64" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>313</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="65" t="s">
+        <v>314</v>
+      </c>
+      <c r="B3" s="44" t="s">
         <v>315</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="65" t="s">
+        <v>317</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>318</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="65" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>320</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="65" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>322</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="65" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="B9" s="44" t="s">
         <v>325</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="65" t="s">
+        <v>326</v>
+      </c>
+      <c r="B10" s="66" t="s">
         <v>327</v>
-      </c>
-      <c r="B10" s="66" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="65" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="63" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="65" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="44" t="s">
         <v>331</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="65" t="s">
+        <v>332</v>
+      </c>
+      <c r="B14" s="44" t="s">
         <v>333</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="44" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="65" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67" t="s">
+        <v>336</v>
+      </c>
+      <c r="B17" s="44" t="s">
         <v>337</v>
-      </c>
-      <c r="B17" s="44" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="65" t="s">
+        <v>338</v>
+      </c>
+      <c r="B18" s="44" t="s">
         <v>339</v>
-      </c>
-      <c r="B18" s="44" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="65" t="s">
+        <v>341</v>
+      </c>
+      <c r="B20" s="44" t="s">
         <v>342</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="65" t="s">
+        <v>343</v>
+      </c>
+      <c r="B21" s="44" t="s">
         <v>344</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="65" t="s">
+        <v>345</v>
+      </c>
+      <c r="B22" s="44" t="s">
         <v>346</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="65" t="s">
+        <v>347</v>
+      </c>
+      <c r="B23" s="44" t="s">
         <v>348</v>
-      </c>
-      <c r="B23" s="44" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="65" t="s">
+        <v>349</v>
+      </c>
+      <c r="B24" s="44" t="s">
         <v>350</v>
-      </c>
-      <c r="B24" s="44" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="68" t="s">
+        <v>351</v>
+      </c>
+      <c r="B25" s="44" t="s">
         <v>352</v>
-      </c>
-      <c r="B25" s="44" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -16063,10 +16046,10 @@
     </row>
     <row r="3">
       <c r="A3" s="70" t="s">
+        <v>353</v>
+      </c>
+      <c r="B3" s="70" t="s">
         <v>354</v>
-      </c>
-      <c r="B3" s="70" t="s">
-        <v>355</v>
       </c>
       <c r="C3" s="69"/>
       <c r="D3" s="69"/>
@@ -16095,10 +16078,10 @@
     </row>
     <row r="4">
       <c r="A4" s="71" t="s">
+        <v>355</v>
+      </c>
+      <c r="B4" s="72" t="s">
         <v>356</v>
-      </c>
-      <c r="B4" s="72" t="s">
-        <v>357</v>
       </c>
       <c r="C4" s="69"/>
       <c r="D4" s="69"/>
@@ -16127,10 +16110,10 @@
     </row>
     <row r="5">
       <c r="A5" s="72" t="s">
+        <v>357</v>
+      </c>
+      <c r="B5" s="72" t="s">
         <v>358</v>
-      </c>
-      <c r="B5" s="72" t="s">
-        <v>359</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" s="69"/>
@@ -16159,10 +16142,10 @@
     </row>
     <row r="6">
       <c r="A6" s="72" t="s">
+        <v>359</v>
+      </c>
+      <c r="B6" s="71" t="s">
         <v>360</v>
-      </c>
-      <c r="B6" s="71" t="s">
-        <v>361</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="69"/>
@@ -16191,10 +16174,10 @@
     </row>
     <row r="7">
       <c r="A7" s="72" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="71" t="s">
         <v>362</v>
-      </c>
-      <c r="B7" s="71" t="s">
-        <v>363</v>
       </c>
       <c r="C7" s="69"/>
       <c r="D7" s="69"/>
@@ -16223,10 +16206,10 @@
     </row>
     <row r="8">
       <c r="A8" s="72" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="71" t="s">
         <v>364</v>
-      </c>
-      <c r="B8" s="71" t="s">
-        <v>365</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="69"/>
@@ -16255,10 +16238,10 @@
     </row>
     <row r="9">
       <c r="A9" s="72" t="s">
+        <v>365</v>
+      </c>
+      <c r="B9" s="71" t="s">
         <v>366</v>
-      </c>
-      <c r="B9" s="71" t="s">
-        <v>367</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="69"/>
@@ -16287,10 +16270,10 @@
     </row>
     <row r="10">
       <c r="A10" s="73" t="s">
+        <v>367</v>
+      </c>
+      <c r="B10" s="71" t="s">
         <v>368</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>369</v>
       </c>
       <c r="C10" s="69"/>
       <c r="D10" s="69"/>
@@ -16319,10 +16302,10 @@
     </row>
     <row r="11">
       <c r="A11" s="71" t="s">
+        <v>369</v>
+      </c>
+      <c r="B11" s="71" t="s">
         <v>370</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>371</v>
       </c>
       <c r="C11" s="69"/>
       <c r="D11" s="69"/>
@@ -16351,10 +16334,10 @@
     </row>
     <row r="12">
       <c r="A12" s="71" t="s">
+        <v>371</v>
+      </c>
+      <c r="B12" s="71" t="s">
         <v>372</v>
-      </c>
-      <c r="B12" s="71" t="s">
-        <v>373</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="69"/>
@@ -16383,10 +16366,10 @@
     </row>
     <row r="13">
       <c r="A13" s="74" t="s">
+        <v>373</v>
+      </c>
+      <c r="B13" s="71" t="s">
         <v>374</v>
-      </c>
-      <c r="B13" s="71" t="s">
-        <v>375</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="69"/>
@@ -16415,10 +16398,10 @@
     </row>
     <row r="14">
       <c r="A14" s="71" t="s">
+        <v>375</v>
+      </c>
+      <c r="B14" s="71" t="s">
         <v>376</v>
-      </c>
-      <c r="B14" s="71" t="s">
-        <v>377</v>
       </c>
       <c r="C14" s="69"/>
       <c r="D14" s="69"/>
@@ -16447,10 +16430,10 @@
     </row>
     <row r="15">
       <c r="A15" s="71" t="s">
+        <v>377</v>
+      </c>
+      <c r="B15" s="71" t="s">
         <v>378</v>
-      </c>
-      <c r="B15" s="71" t="s">
-        <v>379</v>
       </c>
       <c r="C15" s="69"/>
       <c r="D15" s="69"/>
@@ -16479,7 +16462,7 @@
     </row>
     <row r="16">
       <c r="A16" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B16" s="69"/>
       <c r="C16" s="69"/>
@@ -16509,10 +16492,10 @@
     </row>
     <row r="17">
       <c r="A17" s="71" t="s">
+        <v>380</v>
+      </c>
+      <c r="B17" s="71" t="s">
         <v>381</v>
-      </c>
-      <c r="B17" s="71" t="s">
-        <v>382</v>
       </c>
       <c r="C17" s="69"/>
       <c r="D17" s="69"/>
@@ -44092,107 +44075,107 @@
   <sheetData>
     <row r="3">
       <c r="A3" s="63" t="s">
+        <v>382</v>
+      </c>
+      <c r="G3" s="63" t="s">
         <v>383</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="75"/>
       <c r="C4" s="44" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H4" s="75"/>
       <c r="I4" s="44" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="75"/>
       <c r="C5" s="44" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H5" s="75"/>
       <c r="I5" s="44" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="75"/>
       <c r="C6" s="44" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="75"/>
       <c r="C7" s="44" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="63" t="s">
+        <v>390</v>
+      </c>
+      <c r="G10" s="63" t="s">
         <v>391</v>
-      </c>
-      <c r="G10" s="63" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="75"/>
       <c r="C11" s="44" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H11" s="75"/>
       <c r="I11" s="44" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="75"/>
       <c r="C12" s="44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="75"/>
       <c r="C13" s="44" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="75"/>
       <c r="C14" s="44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="63" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="75"/>
       <c r="C18" s="44" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="75"/>
       <c r="C19" s="44" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="75"/>
       <c r="C20" s="44" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="75"/>
       <c r="C21" s="44" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -44216,27 +44199,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="63" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1" s="63" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="C1" s="63" t="s">
         <v>404</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="D1" s="63" t="s">
         <v>405</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="E1" s="63" t="s">
         <v>406</v>
       </c>
-      <c r="E1" s="63" t="s">
+      <c r="F1" s="63" t="s">
         <v>407</v>
-      </c>
-      <c r="F1" s="63" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B2" s="44" t="s">
         <v>48</v>
@@ -44253,10 +44236,10 @@
     </row>
     <row r="3">
       <c r="A3" s="44" t="s">
+        <v>409</v>
+      </c>
+      <c r="B3" s="44" t="s">
         <v>410</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>411</v>
       </c>
       <c r="C3" s="44">
         <v>0.0</v>
@@ -44268,15 +44251,15 @@
         <v>8.0</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="44" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>18</v>
@@ -44288,15 +44271,15 @@
         <v>5.0</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="44" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>71</v>
@@ -44310,10 +44293,10 @@
     </row>
     <row r="6">
       <c r="A6" s="44" t="s">
+        <v>415</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>416</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>417</v>
       </c>
       <c r="C6" s="44">
         <v>0.0</v>
@@ -44345,35 +44328,35 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="63" t="s">
+        <v>417</v>
+      </c>
+      <c r="I2" s="63" t="s">
         <v>418</v>
-      </c>
-      <c r="I2" s="63" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="76"/>
       <c r="C3" s="44" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J3" s="75"/>
       <c r="K3" s="44" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="76"/>
       <c r="C4" s="44" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="76"/>
       <c r="C5" s="44" t="s">
+        <v>422</v>
+      </c>
+      <c r="E5" s="65" t="s">
         <v>423</v>
-      </c>
-      <c r="E5" s="65" t="s">
-        <v>424</v>
       </c>
       <c r="F5" s="44" t="s">
         <v>71</v>
@@ -44382,66 +44365,66 @@
     <row r="6">
       <c r="B6" s="76"/>
       <c r="C6" s="44" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="76"/>
       <c r="C7" s="44" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J7" s="77"/>
       <c r="K7" s="44" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="75"/>
       <c r="C8" s="44" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="63" t="s">
+        <v>428</v>
+      </c>
+      <c r="I12" s="63" t="s">
         <v>429</v>
-      </c>
-      <c r="I12" s="63" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="76"/>
       <c r="C13" s="44" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J13" s="75"/>
       <c r="K13" s="44" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="76"/>
       <c r="C14" s="44" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J14" s="75"/>
       <c r="K14" s="44" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="78"/>
       <c r="C15" s="44" t="s">
+        <v>434</v>
+      </c>
+      <c r="E15" s="65" t="s">
         <v>435</v>
-      </c>
-      <c r="E15" s="65" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="76"/>
       <c r="C16" s="44" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F16" s="79" t="s">
         <v>71</v>
@@ -44450,162 +44433,162 @@
     <row r="17">
       <c r="B17" s="76"/>
       <c r="C17" s="44" t="s">
+        <v>437</v>
+      </c>
+      <c r="E17" s="80" t="s">
         <v>438</v>
-      </c>
-      <c r="E17" s="80" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="76"/>
       <c r="C18" s="44" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="76"/>
       <c r="C19" s="44" t="s">
+        <v>440</v>
+      </c>
+      <c r="I19" s="63" t="s">
         <v>441</v>
-      </c>
-      <c r="I19" s="63" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="76"/>
       <c r="C20" s="44" t="s">
+        <v>442</v>
+      </c>
+      <c r="D20" s="81" t="s">
         <v>443</v>
       </c>
-      <c r="D20" s="81" t="s">
+      <c r="E20" s="80" t="s">
         <v>444</v>
-      </c>
-      <c r="E20" s="80" t="s">
-        <v>445</v>
       </c>
       <c r="F20" s="82">
         <v>0.6458333333333334</v>
       </c>
       <c r="J20" s="76"/>
       <c r="K20" s="44" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="76"/>
       <c r="C21" s="44" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="76"/>
       <c r="C22" s="44" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="76"/>
       <c r="C23" s="44" t="s">
+        <v>448</v>
+      </c>
+      <c r="I23" s="63" t="s">
         <v>449</v>
       </c>
-      <c r="I23" s="63" t="s">
+      <c r="J23" s="44" t="s">
         <v>450</v>
-      </c>
-      <c r="J23" s="44" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="83"/>
       <c r="C24" s="44" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J24" s="84"/>
       <c r="K24" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="25">
       <c r="J25" s="75"/>
       <c r="K25" s="44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="63" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J26" s="75"/>
       <c r="K26" s="44" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="76"/>
       <c r="C27" s="44" t="s">
+        <v>456</v>
+      </c>
+      <c r="K27" s="44" t="s">
         <v>457</v>
-      </c>
-      <c r="K27" s="44" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="76"/>
       <c r="C28" s="44" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="84"/>
       <c r="C29" s="44" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D29" s="85"/>
       <c r="E29" s="80" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="75"/>
       <c r="C30" s="44" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="75"/>
       <c r="C31" s="44" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="75"/>
       <c r="C32" s="44" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="75"/>
       <c r="C33" s="44" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="75"/>
       <c r="C34" s="44" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="63" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="76"/>
       <c r="C38" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="E38" s="65" t="s">
         <v>467</v>
-      </c>
-      <c r="E38" s="65" t="s">
-        <v>468</v>
       </c>
       <c r="F38" s="82">
         <v>0.6041666666666666</v>
@@ -44614,7 +44597,7 @@
     <row r="39">
       <c r="B39" s="76"/>
       <c r="C39" s="44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -44643,12 +44626,12 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="44" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="44" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4">
@@ -44660,175 +44643,175 @@
     <row r="6">
       <c r="B6" s="44"/>
       <c r="G6" s="63" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="86" t="s">
+        <v>472</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>473</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="G7" s="87" t="s">
         <v>474</v>
       </c>
-      <c r="G7" s="87" t="s">
+      <c r="H7" s="87" t="s">
         <v>475</v>
-      </c>
-      <c r="H7" s="87" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="87" t="s">
+        <v>476</v>
+      </c>
+      <c r="H8" s="44" t="s">
         <v>477</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="G9" s="87" t="s">
         <v>479</v>
       </c>
-      <c r="G9" s="87" t="s">
+      <c r="H9" s="44" t="s">
         <v>480</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="88" t="s">
+        <v>481</v>
+      </c>
+      <c r="G10" s="44" t="s">
         <v>482</v>
       </c>
-      <c r="G10" s="44" t="s">
+      <c r="H10" s="44" t="s">
         <v>483</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="89" t="s">
+        <v>484</v>
+      </c>
+      <c r="G11" s="44" t="s">
         <v>485</v>
       </c>
-      <c r="G11" s="44" t="s">
+      <c r="H11" s="44" t="s">
         <v>486</v>
-      </c>
-      <c r="H11" s="44" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="89" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13">
       <c r="G13" s="44" t="s">
+        <v>488</v>
+      </c>
+      <c r="H13" s="44" t="s">
         <v>489</v>
-      </c>
-      <c r="H13" s="44" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="88" t="s">
+        <v>490</v>
+      </c>
+      <c r="G14" s="87" t="s">
         <v>491</v>
       </c>
-      <c r="G14" s="87" t="s">
+      <c r="H14" s="44" t="s">
         <v>492</v>
-      </c>
-      <c r="H14" s="44" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="87" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="87" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="87" t="s">
+        <v>495</v>
+      </c>
+      <c r="D17" s="44" t="s">
         <v>496</v>
-      </c>
-      <c r="D17" s="44" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="18">
       <c r="G18" s="63" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="44" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="88" t="s">
+        <v>499</v>
+      </c>
+      <c r="C20" s="87" t="s">
         <v>500</v>
-      </c>
-      <c r="C20" s="87" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="87" t="s">
+        <v>501</v>
+      </c>
+      <c r="F21" s="88" t="s">
         <v>502</v>
-      </c>
-      <c r="F21" s="88" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="44"/>
       <c r="F22" s="87" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="63" t="s">
+        <v>504</v>
+      </c>
+      <c r="F23" s="87" t="s">
         <v>505</v>
-      </c>
-      <c r="F23" s="87" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="44" t="s">
+        <v>506</v>
+      </c>
+      <c r="F24" s="87" t="s">
         <v>507</v>
-      </c>
-      <c r="F24" s="87" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="25">
       <c r="F25" s="87" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26">
       <c r="F26" s="87" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="63" t="s">
+        <v>510</v>
+      </c>
+      <c r="F27" s="87" t="s">
         <v>511</v>
-      </c>
-      <c r="F27" s="87" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="44" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/data/Comparing_Dynamics (1).xlsx
+++ b/data/Comparing_Dynamics (1).xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1486" uniqueCount="505">
   <si>
     <t>Datset</t>
   </si>
@@ -926,33 +926,6 @@
     <t>crimson-armadillo-507</t>
   </si>
   <si>
-    <t>mild-violet-505</t>
-  </si>
-  <si>
-    <t>sweet-water-504</t>
-  </si>
-  <si>
-    <t>driven-pyramid-503</t>
-  </si>
-  <si>
-    <t>serene-river-502</t>
-  </si>
-  <si>
-    <t>silver-frost-501</t>
-  </si>
-  <si>
-    <t>divine-puddle-500</t>
-  </si>
-  <si>
-    <t>divine-snowball-479</t>
-  </si>
-  <si>
-    <t>vocal-eon-478</t>
-  </si>
-  <si>
-    <t>generous-pine-474</t>
-  </si>
-  <si>
     <t>Train:</t>
   </si>
   <si>
@@ -1005,6 +978,12 @@
   </si>
   <si>
     <t>6thOct_FMNIST_WD0.01_unireps_quench_cka_formatted.ipynb</t>
+  </si>
+  <si>
+    <t>6thOct_WD0.003_unireps_quench_cka_formatted.ipynb</t>
+  </si>
+  <si>
+    <t>most recent quench code</t>
   </si>
   <si>
     <t>Plots:</t>
@@ -1371,9 +1350,6 @@
   </si>
   <si>
     <t>quench low</t>
-  </si>
-  <si>
-    <t>6thOct_WD0.003_unireps_quench_cka_formatted.ipynb</t>
   </si>
   <si>
     <t>generate initial plots</t>
@@ -2279,7 +2255,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:G201" displayName="Table_1" name="Table_1" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="A2:G200" displayName="Table_1" name="Table_1" id="2">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -15199,556 +15175,166 @@
       <c r="G177" s="62"/>
     </row>
     <row r="178">
-      <c r="A178" s="43" t="s">
-        <v>302</v>
-      </c>
-      <c r="B178" s="59">
-        <v>1024.0</v>
-      </c>
-      <c r="C178" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D178" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E178" s="59">
-        <v>49.0</v>
-      </c>
-      <c r="F178" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G178" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A178" s="43"/>
+      <c r="B178" s="59"/>
+      <c r="C178" s="43"/>
+      <c r="D178" s="62"/>
+      <c r="E178" s="59"/>
+      <c r="F178" s="62"/>
+      <c r="G178" s="62"/>
     </row>
     <row r="179">
-      <c r="A179" s="43" t="s">
-        <v>303</v>
-      </c>
-      <c r="B179" s="59">
-        <v>1024.0</v>
-      </c>
-      <c r="C179" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D179" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E179" s="59">
-        <v>39.0</v>
-      </c>
-      <c r="F179" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G179" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A179" s="43"/>
+      <c r="B179" s="59"/>
+      <c r="C179" s="43"/>
+      <c r="D179" s="62"/>
+      <c r="E179" s="59"/>
+      <c r="F179" s="62"/>
+      <c r="G179" s="62"/>
     </row>
     <row r="180">
-      <c r="A180" s="43" t="s">
-        <v>304</v>
-      </c>
-      <c r="B180" s="59">
-        <v>1024.0</v>
-      </c>
-      <c r="C180" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D180" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E180" s="59">
-        <v>29.0</v>
-      </c>
-      <c r="F180" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G180" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A180" s="43"/>
+      <c r="B180" s="59"/>
+      <c r="C180" s="43"/>
+      <c r="D180" s="62"/>
+      <c r="E180" s="59"/>
+      <c r="F180" s="62"/>
+      <c r="G180" s="62"/>
     </row>
     <row r="181">
-      <c r="A181" s="43" t="s">
-        <v>305</v>
-      </c>
-      <c r="B181" s="59">
-        <v>1024.0</v>
-      </c>
-      <c r="C181" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D181" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E181" s="59">
-        <v>19.0</v>
-      </c>
-      <c r="F181" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G181" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A181" s="43"/>
+      <c r="B181" s="59"/>
+      <c r="C181" s="43"/>
+      <c r="D181" s="62"/>
+      <c r="E181" s="59"/>
+      <c r="F181" s="62"/>
+      <c r="G181" s="62"/>
     </row>
     <row r="182">
-      <c r="A182" s="43" t="s">
-        <v>306</v>
-      </c>
-      <c r="B182" s="59">
-        <v>1024.0</v>
-      </c>
-      <c r="C182" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D182" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E182" s="59">
-        <v>19.0</v>
-      </c>
-      <c r="F182" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G182" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A182" s="43"/>
+      <c r="B182" s="59"/>
+      <c r="C182" s="43"/>
+      <c r="D182" s="62"/>
+      <c r="E182" s="59"/>
+      <c r="F182" s="62"/>
+      <c r="G182" s="62"/>
     </row>
     <row r="183">
-      <c r="A183" s="43" t="s">
-        <v>307</v>
-      </c>
-      <c r="B183" s="59">
-        <v>1024.0</v>
-      </c>
-      <c r="C183" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D183" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E183" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F183" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G183" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A183" s="43"/>
+      <c r="B183" s="59"/>
+      <c r="C183" s="43"/>
+      <c r="D183" s="62"/>
+      <c r="E183" s="59"/>
+      <c r="F183" s="62"/>
+      <c r="G183" s="62"/>
     </row>
     <row r="184">
-      <c r="A184" s="43" t="s">
-        <v>271</v>
-      </c>
-      <c r="B184" s="59">
-        <v>256.0</v>
-      </c>
-      <c r="C184" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D184" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E184" s="59">
-        <v>49.0</v>
-      </c>
-      <c r="F184" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G184" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A184" s="43"/>
+      <c r="B184" s="59"/>
+      <c r="C184" s="43"/>
+      <c r="D184" s="62"/>
+      <c r="E184" s="59"/>
+      <c r="F184" s="62"/>
+      <c r="G184" s="62"/>
     </row>
     <row r="185">
-      <c r="A185" s="43" t="s">
-        <v>273</v>
-      </c>
-      <c r="B185" s="59">
-        <v>256.0</v>
-      </c>
-      <c r="C185" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D185" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E185" s="59">
-        <v>39.0</v>
-      </c>
-      <c r="F185" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G185" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A185" s="43"/>
+      <c r="B185" s="59"/>
+      <c r="C185" s="43"/>
+      <c r="D185" s="62"/>
+      <c r="E185" s="59"/>
+      <c r="F185" s="62"/>
+      <c r="G185" s="62"/>
     </row>
     <row r="186">
-      <c r="A186" s="43" t="s">
-        <v>274</v>
-      </c>
-      <c r="B186" s="59">
-        <v>256.0</v>
-      </c>
-      <c r="C186" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D186" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E186" s="59">
-        <v>29.0</v>
-      </c>
-      <c r="F186" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G186" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A186" s="43"/>
+      <c r="B186" s="59"/>
+      <c r="C186" s="43"/>
+      <c r="D186" s="62"/>
+      <c r="E186" s="59"/>
+      <c r="F186" s="62"/>
+      <c r="G186" s="62"/>
     </row>
     <row r="187">
-      <c r="A187" s="43" t="s">
-        <v>275</v>
-      </c>
-      <c r="B187" s="59">
-        <v>256.0</v>
-      </c>
-      <c r="C187" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D187" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E187" s="59">
-        <v>19.0</v>
-      </c>
-      <c r="F187" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G187" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A187" s="43"/>
+      <c r="B187" s="59"/>
+      <c r="C187" s="43"/>
+      <c r="D187" s="62"/>
+      <c r="E187" s="59"/>
+      <c r="F187" s="62"/>
+      <c r="G187" s="62"/>
     </row>
     <row r="188">
-      <c r="A188" s="43" t="s">
-        <v>276</v>
-      </c>
-      <c r="B188" s="59">
-        <v>256.0</v>
-      </c>
-      <c r="C188" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D188" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E188" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F188" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G188" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A188" s="43"/>
+      <c r="B188" s="59"/>
+      <c r="C188" s="43"/>
+      <c r="D188" s="62"/>
+      <c r="E188" s="59"/>
+      <c r="F188" s="62"/>
+      <c r="G188" s="62"/>
     </row>
     <row r="189">
-      <c r="A189" s="43" t="s">
-        <v>277</v>
-      </c>
-      <c r="B189" s="59">
-        <v>128.0</v>
-      </c>
-      <c r="C189" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D189" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E189" s="59">
-        <v>49.0</v>
-      </c>
-      <c r="F189" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G189" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A189" s="43"/>
+      <c r="B189" s="59"/>
+      <c r="C189" s="43"/>
+      <c r="D189" s="62"/>
+      <c r="E189" s="59"/>
+      <c r="F189" s="62"/>
+      <c r="G189" s="62"/>
     </row>
     <row r="190">
-      <c r="A190" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="B190" s="59">
-        <v>128.0</v>
-      </c>
-      <c r="C190" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D190" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E190" s="59">
-        <v>39.0</v>
-      </c>
-      <c r="F190" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G190" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A190" s="43"/>
+      <c r="B190" s="59"/>
+      <c r="C190" s="43"/>
+      <c r="D190" s="62"/>
+      <c r="E190" s="59"/>
+      <c r="F190" s="62"/>
+      <c r="G190" s="62"/>
     </row>
     <row r="191">
-      <c r="A191" s="43" t="s">
-        <v>279</v>
-      </c>
-      <c r="B191" s="59">
-        <v>128.0</v>
-      </c>
-      <c r="C191" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D191" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E191" s="59">
-        <v>29.0</v>
-      </c>
-      <c r="F191" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G191" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A191" s="43"/>
+      <c r="B191" s="59"/>
+      <c r="C191" s="43"/>
+      <c r="D191" s="62"/>
+      <c r="E191" s="59"/>
+      <c r="F191" s="62"/>
+      <c r="G191" s="62"/>
     </row>
     <row r="192">
-      <c r="A192" s="43" t="s">
-        <v>280</v>
-      </c>
-      <c r="B192" s="59">
-        <v>128.0</v>
-      </c>
-      <c r="C192" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D192" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E192" s="59">
-        <v>19.0</v>
-      </c>
-      <c r="F192" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G192" s="62">
-        <v>50000.0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="43" t="s">
-        <v>281</v>
-      </c>
-      <c r="B193" s="59">
-        <v>128.0</v>
-      </c>
-      <c r="C193" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D193" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E193" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F193" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G193" s="62">
-        <v>50000.0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="43" t="s">
-        <v>282</v>
-      </c>
-      <c r="B194" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="C194" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D194" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E194" s="59">
-        <v>49.0</v>
-      </c>
-      <c r="F194" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G194" s="62">
-        <v>50000.0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="43" t="s">
-        <v>283</v>
-      </c>
-      <c r="B195" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="C195" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D195" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E195" s="59">
-        <v>39.0</v>
-      </c>
-      <c r="F195" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G195" s="62">
-        <v>50000.0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="43" t="s">
-        <v>284</v>
-      </c>
-      <c r="B196" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="C196" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D196" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E196" s="59">
-        <v>29.0</v>
-      </c>
-      <c r="F196" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G196" s="62">
-        <v>50000.0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="B197" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="C197" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D197" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E197" s="59">
-        <v>19.0</v>
-      </c>
-      <c r="F197" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G197" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A192" s="43"/>
+      <c r="B192" s="59"/>
+      <c r="C192" s="43"/>
+      <c r="D192" s="62"/>
+      <c r="E192" s="59"/>
+      <c r="F192" s="62"/>
+      <c r="G192" s="62"/>
     </row>
     <row r="198">
-      <c r="A198" s="43" t="s">
-        <v>286</v>
-      </c>
-      <c r="B198" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="C198" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D198" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E198" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F198" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G198" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A198" s="43"/>
+      <c r="B198" s="59"/>
+      <c r="C198" s="43"/>
+      <c r="D198" s="62"/>
+      <c r="E198" s="59"/>
+      <c r="F198" s="62"/>
+      <c r="G198" s="62"/>
     </row>
     <row r="199">
-      <c r="A199" s="43" t="s">
-        <v>308</v>
-      </c>
-      <c r="B199" s="59">
-        <v>128.0</v>
-      </c>
-      <c r="C199" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D199" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E199" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F199" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G199" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A199" s="43"/>
+      <c r="B199" s="59"/>
+      <c r="C199" s="43"/>
+      <c r="D199" s="62"/>
+      <c r="E199" s="59"/>
+      <c r="F199" s="62"/>
+      <c r="G199" s="62"/>
     </row>
     <row r="200">
-      <c r="A200" s="43" t="s">
-        <v>309</v>
-      </c>
-      <c r="B200" s="59">
-        <v>32.0</v>
-      </c>
-      <c r="C200" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D200" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E200" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F200" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G200" s="62">
-        <v>50000.0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="B201" s="59">
-        <v>128.0</v>
-      </c>
-      <c r="C201" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="D201" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="E201" s="59">
-        <v>11.0</v>
-      </c>
-      <c r="F201" s="62">
-        <v>0.0</v>
-      </c>
-      <c r="G201" s="62">
-        <v>50000.0</v>
-      </c>
+      <c r="A200" s="43"/>
+      <c r="B200" s="59"/>
+      <c r="C200" s="43"/>
+      <c r="D200" s="62"/>
+      <c r="E200" s="59"/>
+      <c r="F200" s="62"/>
+      <c r="G200" s="62"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -15771,184 +15357,192 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="63" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="64" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="65" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="63" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="65" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="65" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="65" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="65" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="63" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="65" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="65" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="63" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="65" t="s">
-        <v>330</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>331</v>
+      <c r="A12" s="65" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65" t="s">
-        <v>332</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>333</v>
+      <c r="A14" s="63" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="65" t="s">
+        <v>323</v>
+      </c>
       <c r="B15" s="44" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="65" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="67" t="s">
-        <v>336</v>
-      </c>
       <c r="B17" s="44" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="65" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="63" t="s">
-        <v>340</v>
+      <c r="A19" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="B19" s="44" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="65" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="65" t="s">
-        <v>343</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>344</v>
+      <c r="A21" s="63" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="65" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="65" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="65" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="68" t="s">
-        <v>351</v>
+      <c r="A25" s="65" t="s">
+        <v>340</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>352</v>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65" t="s">
+        <v>342</v>
+      </c>
+      <c r="B26" s="44" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="68" t="s">
+        <v>344</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -15961,19 +15555,20 @@
     <hyperlink r:id="rId6" ref="A8"/>
     <hyperlink r:id="rId7" location="scrollTo=fe94d4fc" ref="A10"/>
     <hyperlink r:id="rId8" location="scrollTo=IaHlVOWXS3O9" ref="A11"/>
-    <hyperlink r:id="rId9" location="scrollTo=y1j2vuQZMpJo" ref="A13"/>
-    <hyperlink r:id="rId10" ref="A14"/>
-    <hyperlink r:id="rId11" location="scrollTo=y1j2vuQZMpJo" ref="A16"/>
-    <hyperlink r:id="rId12" location="scrollTo=1d17f014" ref="A17"/>
-    <hyperlink r:id="rId13" ref="A18"/>
+    <hyperlink r:id="rId9" ref="A12"/>
+    <hyperlink r:id="rId10" location="scrollTo=y1j2vuQZMpJo" ref="A15"/>
+    <hyperlink r:id="rId11" ref="A16"/>
+    <hyperlink r:id="rId12" location="scrollTo=y1j2vuQZMpJo" ref="A18"/>
+    <hyperlink r:id="rId13" location="scrollTo=1d17f014" ref="A19"/>
     <hyperlink r:id="rId14" ref="A20"/>
-    <hyperlink r:id="rId15" ref="A21"/>
-    <hyperlink r:id="rId16" ref="A22"/>
-    <hyperlink r:id="rId17" ref="A23"/>
-    <hyperlink r:id="rId18" ref="A24"/>
-    <hyperlink r:id="rId19" ref="A25"/>
+    <hyperlink r:id="rId15" ref="A22"/>
+    <hyperlink r:id="rId16" ref="A23"/>
+    <hyperlink r:id="rId17" ref="A24"/>
+    <hyperlink r:id="rId18" ref="A25"/>
+    <hyperlink r:id="rId19" ref="A26"/>
+    <hyperlink r:id="rId20" ref="A27"/>
   </hyperlinks>
-  <drawing r:id="rId20"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
 
@@ -16046,10 +15641,10 @@
     </row>
     <row r="3">
       <c r="A3" s="70" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C3" s="69"/>
       <c r="D3" s="69"/>
@@ -16078,10 +15673,10 @@
     </row>
     <row r="4">
       <c r="A4" s="71" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B4" s="72" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C4" s="69"/>
       <c r="D4" s="69"/>
@@ -16110,10 +15705,10 @@
     </row>
     <row r="5">
       <c r="A5" s="72" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B5" s="72" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" s="69"/>
@@ -16142,10 +15737,10 @@
     </row>
     <row r="6">
       <c r="A6" s="72" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B6" s="71" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C6" s="69"/>
       <c r="D6" s="69"/>
@@ -16174,10 +15769,10 @@
     </row>
     <row r="7">
       <c r="A7" s="72" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="C7" s="69"/>
       <c r="D7" s="69"/>
@@ -16206,10 +15801,10 @@
     </row>
     <row r="8">
       <c r="A8" s="72" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B8" s="71" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="69"/>
@@ -16238,10 +15833,10 @@
     </row>
     <row r="9">
       <c r="A9" s="72" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C9" s="69"/>
       <c r="D9" s="69"/>
@@ -16270,10 +15865,10 @@
     </row>
     <row r="10">
       <c r="A10" s="73" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="C10" s="69"/>
       <c r="D10" s="69"/>
@@ -16302,10 +15897,10 @@
     </row>
     <row r="11">
       <c r="A11" s="71" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C11" s="69"/>
       <c r="D11" s="69"/>
@@ -16334,10 +15929,10 @@
     </row>
     <row r="12">
       <c r="A12" s="71" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="69"/>
@@ -16366,10 +15961,10 @@
     </row>
     <row r="13">
       <c r="A13" s="74" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C13" s="69"/>
       <c r="D13" s="69"/>
@@ -16398,10 +15993,10 @@
     </row>
     <row r="14">
       <c r="A14" s="71" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C14" s="69"/>
       <c r="D14" s="69"/>
@@ -16430,10 +16025,10 @@
     </row>
     <row r="15">
       <c r="A15" s="71" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C15" s="69"/>
       <c r="D15" s="69"/>
@@ -16462,7 +16057,7 @@
     </row>
     <row r="16">
       <c r="A16" s="71" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B16" s="69"/>
       <c r="C16" s="69"/>
@@ -16492,10 +16087,10 @@
     </row>
     <row r="17">
       <c r="A17" s="71" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C17" s="69"/>
       <c r="D17" s="69"/>
@@ -44075,107 +43670,107 @@
   <sheetData>
     <row r="3">
       <c r="A3" s="63" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G3" s="63" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="75"/>
       <c r="C4" s="44" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="H4" s="75"/>
       <c r="I4" s="44" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="75"/>
       <c r="C5" s="44" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="H5" s="75"/>
       <c r="I5" s="44" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="75"/>
       <c r="C6" s="44" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="75"/>
       <c r="C7" s="44" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="63" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="G10" s="63" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="75"/>
       <c r="C11" s="44" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="H11" s="75"/>
       <c r="I11" s="44" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="75"/>
       <c r="C12" s="44" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="75"/>
       <c r="C13" s="44" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="75"/>
       <c r="C14" s="44" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="63" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="75"/>
       <c r="C18" s="44" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="75"/>
       <c r="C19" s="44" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="75"/>
       <c r="C20" s="44" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="75"/>
       <c r="C21" s="44" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -44199,27 +43794,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="63" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B1" s="63" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="C1" s="63" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D1" s="63" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="E1" s="63" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="F1" s="63" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="44" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B2" s="44" t="s">
         <v>48</v>
@@ -44236,10 +43831,10 @@
     </row>
     <row r="3">
       <c r="A3" s="44" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C3" s="44">
         <v>0.0</v>
@@ -44251,15 +43846,15 @@
         <v>8.0</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="44" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>18</v>
@@ -44271,15 +43866,15 @@
         <v>5.0</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="44" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>71</v>
@@ -44293,10 +43888,10 @@
     </row>
     <row r="6">
       <c r="A6" s="44" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="C6" s="44">
         <v>0.0</v>
@@ -44328,35 +43923,35 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="63" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="I2" s="63" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="76"/>
       <c r="C3" s="44" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="J3" s="75"/>
       <c r="K3" s="44" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="76"/>
       <c r="C4" s="44" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="76"/>
       <c r="C5" s="44" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="E5" s="65" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="F5" s="44" t="s">
         <v>71</v>
@@ -44365,66 +43960,66 @@
     <row r="6">
       <c r="B6" s="76"/>
       <c r="C6" s="44" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="76"/>
       <c r="C7" s="44" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="J7" s="77"/>
       <c r="K7" s="44" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="75"/>
       <c r="C8" s="44" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="63" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="I12" s="63" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="76"/>
       <c r="C13" s="44" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="J13" s="75"/>
       <c r="K13" s="44" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="76"/>
       <c r="C14" s="44" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="J14" s="75"/>
       <c r="K14" s="44" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="78"/>
       <c r="C15" s="44" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="E15" s="65" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="76"/>
       <c r="C16" s="44" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="F16" s="79" t="s">
         <v>71</v>
@@ -44433,162 +44028,162 @@
     <row r="17">
       <c r="B17" s="76"/>
       <c r="C17" s="44" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="E17" s="80" t="s">
-        <v>438</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="76"/>
       <c r="C18" s="44" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="76"/>
       <c r="C19" s="44" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="I19" s="63" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="76"/>
       <c r="C20" s="44" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="D20" s="81" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="E20" s="80" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F20" s="82">
         <v>0.6458333333333334</v>
       </c>
       <c r="J20" s="76"/>
       <c r="K20" s="44" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="76"/>
       <c r="C21" s="44" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="76"/>
       <c r="C22" s="44" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="76"/>
       <c r="C23" s="44" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I23" s="63" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="J23" s="44" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="83"/>
       <c r="C24" s="44" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="J24" s="84"/>
       <c r="K24" s="44" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25">
       <c r="J25" s="75"/>
       <c r="K25" s="44" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="63" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="J26" s="75"/>
       <c r="K26" s="44" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="76"/>
       <c r="C27" s="44" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="K27" s="44" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="76"/>
       <c r="C28" s="44" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="84"/>
       <c r="C29" s="44" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="D29" s="85"/>
       <c r="E29" s="80" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="75"/>
       <c r="C30" s="44" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="75"/>
       <c r="C31" s="44" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="75"/>
       <c r="C32" s="44" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="75"/>
       <c r="C33" s="44" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="75"/>
       <c r="C34" s="44" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="63" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="76"/>
       <c r="C38" s="44" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="E38" s="65" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F38" s="82">
         <v>0.6041666666666666</v>
@@ -44597,7 +44192,7 @@
     <row r="39">
       <c r="B39" s="76"/>
       <c r="C39" s="44" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -44626,12 +44221,12 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="44" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="44" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4">
@@ -44643,175 +44238,175 @@
     <row r="6">
       <c r="B6" s="44"/>
       <c r="G6" s="63" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="86" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="G7" s="87" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="H7" s="87" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="87" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="H8" s="44" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="44" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="G9" s="87" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="H9" s="44" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="88" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="H10" s="44" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="89" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="H11" s="44" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="89" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13">
       <c r="G13" s="44" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="88" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="G14" s="87" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="87" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="87" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="87" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18">
       <c r="G18" s="63" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="19">
       <c r="H19" s="44" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="88" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="87" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="F21" s="88" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="44"/>
       <c r="F22" s="87" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="63" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="F23" s="87" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="44" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="F24" s="87" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="25">
       <c r="F25" s="87" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26">
       <c r="F26" s="87" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="63" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="F27" s="87" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="44" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
